--- a/Teorie/2.IT/APP/EXCEL VYUKA.xlsx
+++ b/Teorie/2.IT/APP/EXCEL VYUKA.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it-martinsramek\Downloads\SCMSD-IT-Martin-Sramek\Teorie\2.IT\APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB4E61-3062-4627-8E35-EE5AD8AAC497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A04E76B-C4FE-41CD-9D15-659D9B4FE23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Úvod" sheetId="1" r:id="rId1"/>
     <sheet name="prostředí" sheetId="4" r:id="rId2"/>
     <sheet name="vzorce" sheetId="5" r:id="rId3"/>
-    <sheet name="Řady" sheetId="2" r:id="rId4"/>
-    <sheet name="Formát" sheetId="3" r:id="rId5"/>
+    <sheet name="priklady" sheetId="6" r:id="rId4"/>
+    <sheet name="vzorce 2" sheetId="7" r:id="rId5"/>
+    <sheet name="Řady" sheetId="2" r:id="rId6"/>
+    <sheet name="Formát" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
   <si>
     <t>Výuka Aplikačního programu MS Excel</t>
   </si>
@@ -225,19 +227,69 @@
   </si>
   <si>
     <t>lavice</t>
+  </si>
+  <si>
+    <t>Místo</t>
+  </si>
+  <si>
+    <t>Delka strany</t>
+  </si>
+  <si>
+    <t>Plocha</t>
+  </si>
+  <si>
+    <t>Cena pozemku</t>
+  </si>
+  <si>
+    <t>Venkov</t>
+  </si>
+  <si>
+    <t>Male město</t>
+  </si>
+  <si>
+    <t>Predmesti prah</t>
+  </si>
+  <si>
+    <t>Centum prahy</t>
+  </si>
+  <si>
+    <t>Cena za 1m²</t>
+  </si>
+  <si>
+    <t>delka obdelnika strana A</t>
+  </si>
+  <si>
+    <t>delka obdelnika strana B</t>
+  </si>
+  <si>
+    <t>vyska pletiva</t>
+  </si>
+  <si>
+    <t>cena za 1. metr</t>
+  </si>
+  <si>
+    <t>obvod obdelnika</t>
+  </si>
+  <si>
+    <t>plocha pletiva</t>
+  </si>
+  <si>
+    <t>cena plativa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;Kč&quot;_-;\-* #,##0.00\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0\ [$Kč-405]_-;\-* #,##0\ [$Kč-405]_-;_-* &quot;-&quot;??\ [$Kč-405]_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0\ &quot;Kč&quot;_-;\-* #,##0\ &quot;Kč&quot;_-;_-* &quot;-&quot;??\ &quot;Kč&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ [$Kč-405]_-;\-* #,##0.00\ [$Kč-405]_-;_-* &quot;-&quot;??\ [$Kč-405]_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -300,7 +352,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +388,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -368,7 +432,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -408,6 +472,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Čárka" xfId="1" builtinId="3"/>
@@ -1217,7 +1290,7 @@
       <c r="E24" s="19">
         <v>0.75</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="23">
         <f>E24/B24</f>
         <v>3.4090909090909088E-2</v>
       </c>
@@ -1237,6 +1310,193 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0F8197-57DB-4ECD-9A1E-20A5552A0A1D}">
+  <dimension ref="A4:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="24">
+        <v>60</v>
+      </c>
+      <c r="C5" s="28">
+        <f>B5*B5</f>
+        <v>3600</v>
+      </c>
+      <c r="D5" s="25">
+        <v>500</v>
+      </c>
+      <c r="E5" s="29">
+        <f>D5*C5</f>
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="24">
+        <v>45</v>
+      </c>
+      <c r="C6" s="28">
+        <f t="shared" ref="C6:C8" si="0">B6*B6</f>
+        <v>2025</v>
+      </c>
+      <c r="D6" s="25">
+        <v>800</v>
+      </c>
+      <c r="E6" s="29">
+        <f t="shared" ref="E6:E8" si="1">D6*C6</f>
+        <v>1620000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="24">
+        <v>28</v>
+      </c>
+      <c r="C7" s="28">
+        <f t="shared" si="0"/>
+        <v>784</v>
+      </c>
+      <c r="D7" s="25">
+        <v>1100</v>
+      </c>
+      <c r="E7" s="29">
+        <f t="shared" si="1"/>
+        <v>862400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="24">
+        <v>16</v>
+      </c>
+      <c r="C8" s="28">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="D8" s="25">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="29">
+        <f t="shared" si="1"/>
+        <v>563200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BAC55A-6EF2-402E-A021-774B76A3325D}">
+  <dimension ref="A3:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="24">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="28">
+        <f>2*(B3+B4)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="28">
+        <f>B8*B5</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="28">
+        <f>B6*B9</f>
+        <v>14000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1516,7 +1776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
